--- a/data/topfruitspublic.xlsx
+++ b/data/topfruitspublic.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakob\Code\workshops\wsquarto\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C16C2C15-AD13-4376-8968-D5E3FFE92FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,127 +27,127 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="42">
   <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">diet_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">second</t>
-  </si>
-  <si>
-    <t xml:space="preserve">third</t>
-  </si>
-  <si>
-    <t xml:space="preserve">first_confidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">second_confidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">third_confidence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reasoning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seasonal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">distaste</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vegetarian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">himberre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">erdbeere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ananas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kirsche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">honigmelone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">brombeere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d</t>
-  </si>
-  <si>
-    <t xml:space="preserve">weintraube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">taste / texture</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kiwi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">omnivore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mango</t>
-  </si>
-  <si>
-    <t xml:space="preserve">asthetics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">schwarze johannisbeere</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aprikose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">banane</t>
-  </si>
-  <si>
-    <t xml:space="preserve">guave</t>
-  </si>
-  <si>
-    <t xml:space="preserve">h</t>
-  </si>
-  <si>
-    <t xml:space="preserve">j</t>
+    <t>name</t>
+  </si>
+  <si>
+    <t>age</t>
+  </si>
+  <si>
+    <t>gender</t>
+  </si>
+  <si>
+    <t>diet_type</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>first</t>
+  </si>
+  <si>
+    <t>second</t>
+  </si>
+  <si>
+    <t>third</t>
+  </si>
+  <si>
+    <t>first_confidence</t>
+  </si>
+  <si>
+    <t>second_confidence</t>
+  </si>
+  <si>
+    <t>third_confidence</t>
+  </si>
+  <si>
+    <t>reasoning</t>
+  </si>
+  <si>
+    <t>seasonal</t>
+  </si>
+  <si>
+    <t>distaste</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>vegetarian</t>
+  </si>
+  <si>
+    <t>himberre</t>
+  </si>
+  <si>
+    <t>erdbeere</t>
+  </si>
+  <si>
+    <t>ananas</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>kirsche</t>
+  </si>
+  <si>
+    <t>honigmelone</t>
+  </si>
+  <si>
+    <t>c</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>brombeere</t>
+  </si>
+  <si>
+    <t>d</t>
+  </si>
+  <si>
+    <t>weintraube</t>
+  </si>
+  <si>
+    <t>taste / texture</t>
+  </si>
+  <si>
+    <t>kiwi</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>omnivore</t>
+  </si>
+  <si>
+    <t>mango</t>
+  </si>
+  <si>
+    <t>asthetics</t>
+  </si>
+  <si>
+    <t>schwarze johannisbeere</t>
+  </si>
+  <si>
+    <t>aprikose</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t>banane</t>
+  </si>
+  <si>
+    <t>guave</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>j</t>
   </si>
   <si>
     <t xml:space="preserve">practicality </t>
@@ -151,32 +156,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -188,7 +175,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -196,97 +183,78 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0e2841"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e8e8e8"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="e97132"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196b24"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0f9ed5"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="a02b93"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4ea72e"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
         <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607d"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -318,7 +286,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -342,7 +310,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -402,286 +370,282 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N10"/>
-  <sheetFormatPr defaultColWidth="10.79296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="0" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1">
         <v>46101</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3">
         <v>27</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="0" t="n">
+      <c r="E3" s="1">
         <v>46101</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4">
         <v>26</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1">
         <v>46101</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" t="s">
         <v>18</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" t="s">
         <v>25</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5">
         <v>27</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="0" t="n">
+      <c r="E5" s="1">
         <v>46101</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" t="s">
         <v>25</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" t="s">
         <v>19</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="L5" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="0" t="s">
+      <c r="N5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6">
         <v>44</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="0" t="n">
+      <c r="E6" s="1">
         <v>46105</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" t="s">
         <v>18</v>
       </c>
-      <c r="L6" s="0" t="s">
+      <c r="L6" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="0" t="s">
+      <c r="D7" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="0" t="n">
+      <c r="E7" s="1">
         <v>46105</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="0" t="s">
+      <c r="G7" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="H7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8">
         <v>30</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="0" t="s">
+      <c r="D8" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="0" t="n">
+      <c r="E8" s="1">
         <v>46105</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="0" t="s">
+      <c r="G8" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="0" t="s">
+      <c r="H8" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="0" t="s">
+      <c r="D9" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="E9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10">
         <v>27</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="0" t="s">
+      <c r="D10" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="0" t="s">
+      <c r="E10" s="1"/>
+      <c r="L10" t="s">
         <v>41</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.7875" bottom="0.7875" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>